--- a/data/raw/inventory/Week 33/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 33/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1143,7 +1143,7 @@
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>31</v>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F15" t="n">
         <v>116</v>
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>76</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
@@ -2507,7 +2507,7 @@
         <v>208</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34" t="n">
         <v>140</v>
@@ -2519,13 +2519,13 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>217</v>
+      </c>
+      <c r="L34" t="n">
         <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>218</v>
-      </c>
-      <c r="L34" t="n">
-        <v>10</v>
       </c>
       <c r="M34" t="n">
         <v>1</v>
